--- a/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="51">
   <si>
     <t>event</t>
   </si>
@@ -115,19 +115,19 @@
     <t>sound: shout(0-156), sound: shout(204-240), sound: gunshot_or_explosion(48-72), sound: impact(108-216), visual: carrying(216-216), visual: carrying(168-168), visual: carrying(192-192), visual: carrying(120-120)</t>
   </si>
   <si>
-    <t>sound: impact(0-36), sound: impact(60-96), sound: impact(120-216), sound: shout(24-72), sound: shout(216-240), sound: gunshot_or_explosion(84-132), sound: gunshot_or_explosion(168-228), visual: carrying(168-192), visual: explosion_visible(144-240), visual: explosion_visible(168-168), visual: explosion_visible(192-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: running(120-144), visual: running(144-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(120-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(120-240)</t>
-  </si>
-  <si>
-    <t>sound: impact(0-60), sound: impact(192-240), sound: shout(24-48), sound: shout(72-192), sound: gunshot_or_explosion(48-84), sound: horn(180-204), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: suspicious_near_vehicle(72-120), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(72-72)</t>
-  </si>
-  <si>
-    <t>sound: shout(0-24), sound: shout(48-240), sound: impact(12-60), sound: gunshot_or_explosion(108-144), sound: gunshot_or_explosion(192-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-240), visual: gunshot_visible(120-240), visual: running(120-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(144-216)</t>
+    <t>sound: impact(0-216), sound: shout(24-72), sound: shout(216-240), sound: gunshot_or_explosion(84-132), sound: gunshot_or_explosion(168-228), visual: carrying(168-192), visual: explosion_visible(144-240), visual: explosion_visible(168-168), visual: explosion_visible(192-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: running(120-144), visual: running(144-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(120-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(120-240)</t>
+  </si>
+  <si>
+    <t>sound: impact(0-60), sound: impact(192-240), sound: shout(24-192), sound: gunshot_or_explosion(48-84), sound: horn(180-204), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: suspicious_near_vehicle(72-120), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(72-72)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-240), sound: impact(12-60), sound: gunshot_or_explosion(108-144), sound: gunshot_or_explosion(192-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-240), visual: gunshot_visible(120-240), visual: running(120-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(144-216)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-36), sound: impact(24-60), sound: impact(120-144), sound: impact(180-204), sound: engine(48-96), sound: engine(168-228), sound: shout(84-240), visual: explosion_visible(120-120), visual: explosion_visible(120-120), visual: explosion_visible(48-48), visual: explosion_visible(168-168), visual: explosion_visible(24-240), visual: explosion_visible(120-240), visual: explosion_visible(192-240), visual: running(48-240), visual: running(120-240), visual: running(120-240)</t>
   </si>
   <si>
-    <t>sound: engine(0-24), sound: impact(12-108), sound: impact(132-156), sound: gunshot_or_explosion(24-48), sound: gunshot_or_explosion(120-144), sound: shout(96-240), visual: enter_or_exit_vehicle(0-24), visual: explosion_visible(48-240), visual: explosion_visible(144-240), visual: explosion_visible(48-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: running(144-240), visual: suspicious_near_vehicle(0-24), visual: vehicle_collision(0-240)</t>
+    <t>sound: engine(0-24), sound: impact(12-156), sound: gunshot_or_explosion(24-48), sound: gunshot_or_explosion(120-144), sound: shout(96-240), visual: enter_or_exit_vehicle(0-24), visual: explosion_visible(48-240), visual: explosion_visible(144-240), visual: explosion_visible(48-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: running(144-240), visual: suspicious_near_vehicle(0-24), visual: vehicle_collision(0-240)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: impact(12-144), sound: impact(180-240), sound: shout(132-192), sound: tire_squeal(156-180), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(168-168)</t>
@@ -136,16 +136,16 @@
     <t>sound: shout(0-84), sound: impact(72-96), sound: impact(216-240), sound: engine(84-228), sound: tire_squeal(180-216)</t>
   </si>
   <si>
-    <t>sound: shout(0-72), sound: shout(96-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-96), sound: engine(120-204), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(168-168), visual: vehicle_collision(168-168)</t>
-  </si>
-  <si>
-    <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-180), sound: shout(204-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144), visual: carrying(48-48), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96)</t>
+    <t>sound: shout(0-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-204), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(168-168), visual: vehicle_collision(168-168)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144), visual: carrying(48-48), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: impact(12-108), sound: impact(204-240), sound: tire_squeal(24-48), sound: shout(36-60), sound: shout(120-216), sound: gunshot_or_explosion(96-132), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
-    <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-84), sound: shout(108-168), sound: impact(72-240), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
+    <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-168), sound: impact(72-240), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(24-48), visual: enter_or_exit_vehicle(192-216), visual: suspicious_near_vehicle(24-144), visual: suspicious_near_vehicle(168-216)</t>
@@ -166,13 +166,13 @@
     <t>visual: carrying(0-0), visual: carrying(120-192), visual: carrying(48-96), visual: carrying(72-72), visual: carrying(24-24), visual: carrying(144-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
-    <t>sound: shout(0-228), sound: impact(132-156), sound: impact(180-240), visual: physical_altercation(48-120), visual: physical_altercation(144-168)</t>
-  </si>
-  <si>
-    <t>sound: shout(0-216), sound: gunshot_or_explosion(120-144), sound: impact(156-180), sound: impact(204-240), visual: physical_altercation(48-120), visual: running(24-120), visual: running(192-192), visual: running(24-120), visual: running(192-192)</t>
-  </si>
-  <si>
-    <t>sound: impact(0-144), sound: impact(180-228), sound: shout(12-48), sound: shout(144-192), sound: shout(216-240), sound: gunshot_or_explosion(108-132), sound: tire_squeal(132-156), visual: carrying(48-72), visual: carrying(0-24), visual: carrying(120-144), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-48)</t>
+    <t>sound: shout(0-228), sound: impact(132-240), visual: physical_altercation(48-120), visual: physical_altercation(144-168)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-216), sound: gunshot_or_explosion(120-144), sound: impact(156-240), visual: physical_altercation(48-120), visual: running(24-120), visual: running(192-192), visual: running(24-120), visual: running(192-192)</t>
+  </si>
+  <si>
+    <t>sound: impact(0-144), sound: impact(180-228), sound: shout(12-48), sound: shout(144-240), sound: gunshot_or_explosion(108-132), sound: tire_squeal(132-156), visual: carrying(48-72), visual: carrying(0-24), visual: carrying(120-144), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-48)</t>
   </si>
   <si>
     <t>sound: impact(0-24), sound: impact(72-144), sound: impact(192-240), sound: shout(12-192), sound: engine(180-204), visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
@@ -184,7 +184,7 @@
     <t>sound: engine(0-24), sound: horn(12-72), sound: impact(60-240), sound: gunshot_or_explosion(84-120), sound: shout(120-144), visual: 9(216-216), visual: 9(216-216), visual: enter_or_exit_vehicle(168-216), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-240), visual: vehicle_collision(144-144), visual: vehicle_collision(96-120), visual: vehicle_collision(192-240), visual: vehicle_collision(72-72), visual: vehicle_collision(168-168)</t>
   </si>
   <si>
-    <t>sound: tire_squeal(0-24), sound: shout(12-48), sound: shout(84-132), sound: shout(156-216), sound: gunshot_or_explosion(36-60), sound: impact(48-96), sound: impact(120-240), visual: enter_or_exit_vehicle(168-168), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-120), visual: vehicle_collision(72-240)</t>
+    <t>sound: tire_squeal(0-24), sound: shout(12-48), sound: shout(84-216), sound: gunshot_or_explosion(36-60), sound: impact(48-240), visual: enter_or_exit_vehicle(168-168), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-120), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
     <t>visual: carrying(0-24), visual: carrying(48-192), visual: enter_or_exit_vehicle(72-144), visual: running(216-216), visual: suspicious_near_vehicle(0-216)</t>
@@ -588,19 +588,19 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="C2">
         <v>0.6</v>
       </c>
       <c r="D2">
-        <v>0.545</v>
+        <v>0.667</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1708,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1750,7 +1750,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1759,23 +1759,6 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2084,7 +2067,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2126,7 +2109,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2135,23 +2118,6 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>23</v>
       </c>
     </row>

--- a/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>sound: engine(0-24), sound: impact(12-108), sound: impact(204-240), sound: tire_squeal(24-48), sound: shout(36-60), sound: shout(120-216), sound: gunshot_or_explosion(96-132), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-168), sound: impact(72-240), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -973,7 +976,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1032,15 +1035,32 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1085,7 +1105,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1123,13 +1143,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1173,7 +1193,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1234,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1278,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1366,7 +1386,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1410,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1454,7 +1474,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1498,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1515,7 +1535,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1576,7 +1596,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1637,7 +1657,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1701,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1698,7 +1718,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1762,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1759,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1803,7 +1823,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1847,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +1972,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +2016,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
